--- a/海外客诉台账_标准化数据.xlsx
+++ b/海外客诉台账_标准化数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客诉明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="客诉明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="数据字典" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG72"/>
+  <dimension ref="A1:AG74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8458,6 +8458,14 @@
       <c r="G57" s="2" t="n">
         <v>46189</v>
       </c>
+      <c r="H57" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>柜机</t>
@@ -8493,7 +8501,55 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>未结案</t>
+          <t>结案</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>（1）电机供应商制程环节电批扭力参数管控不到位，力矩设定参数偏大时，员工操作时会导致部分电机螺钉柱打滑牙；
+2）螺钉柱滑牙后电机后盖结合力会下降，装配整机后经过多次装、卸及海外长途运输颠簸后出现后盖脱开，造成转子不同心，整机通电后电机不转动报E6故障代码。</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1.所有电机紧固螺钉统一工艺力矩标准≤2.0N·m；产线每日开班前，品质人员对风批扭矩设备做参数点检、定期校准，杜绝力矩过大造成螺柱滑牙。
+2.电机整机下线后，不允许开盖二次合盖返修；若拆解后盖，整机直接报废，从源头规避重复锁螺钉导致螺柱滑牙风险。
+3.切换通得电机方案，重新进行样品确认及内、外销整机认证报备；</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>供应商大洋</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>部品不良</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>黄敬阳</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>方案还需验证，延期到7月10号完成</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -8505,22 +8561,22 @@
         <v>6</v>
       </c>
       <c r="AB57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -8829,7 +8885,46 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>未结案</t>
+          <t>结案</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1、个别检验员作业要求不清晰，作业标准不明确，存在明显的主观作业意识；
+2、称重设备与检验数据录入设备脱节，无法有效绑定，存在主观调整数据的隐患；
+3、检验系统数据上传填写缺乏真正的双人复核机制；
+4、多基地作业标准要求未实时拉通，导致在执行层面出现偏差；
+综合以上，导致系统填写数据与产品称重数据失真。
+</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 对标中山拉通标准修订《OQC检验作业指导书》相关要求 陈国峰 6月26日
+2 建立室内外机检验拍照要求；实行检验平板相机水印+QMS系统水印双结合，防止检验弄虚作假 陈国峰 6月25日
+3 建立检验记录稽查机制，专人每天稽查留档资料的符合性 罗祖壮/蒋桂龙 6月25日
+4 研究增加检验增加拍照直接取数填写功能，减少人员干预影响 严林贵/陈国峰 待定
+</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>黄敬阳</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>有</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -8841,22 +8936,22 @@
         <v>6</v>
       </c>
       <c r="AB60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -9331,6 +9426,14 @@
       <c r="G64" s="2" t="n">
         <v>46206</v>
       </c>
+      <c r="H64" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>变频整机</t>
@@ -9368,12 +9471,53 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>未结案</t>
+          <t>结案</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>补发面板更换</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.生产此订单面板时，因防呆块放置在左侧，丝印商标位置在右上角，面板放反情况下，丝印位置是平整的，在丝印时存在放反后能够正常丝印的情况
+2.商标印反后的面板转移至皮带线上时，员工同时将面板拿反，因770T面板正反放置无法从表面进行区分，导致终检未能检出，不良流出。
+3、面板装配后，异常机商标位于面板右上角与图纸位置不一致，可以通过目视检出，检验员漏检此商标导致不良流出。
+</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1、新增临时管控要求防呆块必须放置在丝印商标位置下方（与面板脚链对齐）。——卢干要/张建林  立即执行
+    2、丝印首检时同步检查防呆块的放置位置，每批次做检查通报。——张建林  立即执行
+    4、组织检验员岗位进行案例培训，并重新验收检验员的检验基础能力。——张建林/肖旭  持续进行
+    3、针对770T该款面板工艺设计新型的防呆工装。——刘斌  2026/7/15</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>中山二厂</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>装配问题</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>黄敬阳</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -9385,22 +9529,22 @@
         <v>6</v>
       </c>
       <c r="AB64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -9430,6 +9574,14 @@
       </c>
       <c r="G65" s="2" t="n">
         <v>46209</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -9466,12 +9618,51 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>未结案</t>
+          <t>结案</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>派人现场返包</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>因A/B/C线圈摆放较近，员工贴标时未仔细核对导致贴错，导致生产时电子膨胀阀防错位置</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 拖多预装设置专属区域，并固定人员预装。物料针对拖多生产线体（W3/W7/W13）电子膨胀阀线圈预装划分区域，增加工装台，并安排固定人员预装；预装完成后在线边按照A、B、C分箱摆放，并增加明显标贴。
+2 改造完成前增加1人专检拖多电子膨胀阀是否套错位置
+3 更改工艺拖多套线圈员工排岗，线上每人最多套两个线圈，拖三以上机型禁止一人套3个线圈。
+4 针对W3、W7拖多电子膨胀阀线圈套错无法拦截问题，标准机液管增加感温包识别温度差判断电子膨胀阀线圈是否套错，并要求研发新增机型时，对商检配套检验增加点检。
+</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>中山一厂</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>装配问题</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>黄敬阳</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>有</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -9483,22 +9674,22 @@
         <v>6</v>
       </c>
       <c r="AB65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -9528,6 +9719,14 @@
       </c>
       <c r="G66" s="2" t="n">
         <v>46209</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -9564,12 +9763,36 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>未结案</t>
+          <t>结案</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>补发物料</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1.供应商端风轮做动平衡时，员工为了提高效率加平衡片后未开机，重新测试风轮平衡量，存在生产流程漏洞，导致不良流出
+2.品质部入仓和出货检验抽检时未发现不良，导致不良品流出</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1、完善风轮动平衡测试操作流程规范，增加加动平衡片后重新测试动平衡量流程，同时对该产品的动平衡工序进行定人定机顶岗，便于责任追溯。
+2、在动平衡机台上方安装了监控摄像头，全天候监督员工规范操作，即监督员工严格执行动平衡测试加平衡片后再开机测试，最后滴加胶水的规范操作(如下图) 
+3、同步对跳动大不良问题举一反三：车间已规定专人专岗测量，并制定了严厉的考核制度执行，同时品质部全程做监督，并对测量产品进行抽查，防止不良流出。
+</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>供应商</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>部品不良</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -9581,22 +9804,22 @@
         <v>6</v>
       </c>
       <c r="AB66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -9626,6 +9849,14 @@
       </c>
       <c r="G67" s="2" t="n">
         <v>46210</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -9665,12 +9896,55 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>未结案</t>
+          <t>结案</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>快递物料</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">因未见实物，根据图片初步分析可能导致料带断裂的原因为
+1、载带卷封合压力过大，导致封带粘接过牢，难以剥离。
+2、目前客户反馈不良数量为1盘，排查其他客户均未反馈同类问题，推测该问题产生于芯片编带设备开机初期，作业人员手动调整封合参数阶段。
+</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>调整生产机制：目前要求调机使用空盘调试，调试产出的载带全部报废;待设备封合参数完全稳定后，确认合格才正常使用带产品批量生产；</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>万颗子</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>电控</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
           <t>黄敬阳</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>该案子因无样品进行分析，给出的是可能原因及对应整改措施</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
@@ -9682,22 +9956,22 @@
         <v>6</v>
       </c>
       <c r="AB67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -9727,6 +10001,14 @@
       </c>
       <c r="G68" s="2" t="n">
         <v>46213</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>46208</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -9771,7 +10053,73 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>未结案</t>
+          <t>结案</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自动焊漏：弯头插配间隙，管口清洁度，枪排堵塞等造成焊接火焰波动不稳定，导致焊点未有效渗透，氦检员工检验失效导致不良品流出
+手工焊漏：焊点加热时间过长、两器返修人员不符上岗资质导致过烧泄露
+长U管泄露：厂家来料喷墨黑管（不良）使用导致泄露
+端板刺穿：两器端板来料毛刺长度不合格或生产过程摔机、碰撞导致端板变形刺穿铜管
+手工切割泄漏：原我司采用手工机械切割方式，无法在切割过程对两器进行有效限位，员工容易出现切偏等风险导致切割泄漏
+四通阀来料：四通阀供应商（盾安、三花等）生产加工焊接微漏不良，我司生产、打包过程肉眼无法识别导致不良品流出
+</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>每台胀管机喇叭口成型、管口高度以及长U机每台机长U管开料长度每日专项稽查通报，从加工工艺性上提升焊接稳定性
+气)，保证管口清洁度，减少铜粉、铝屑残留
+焊接上线增加风刀吹扫(露点小于-20摄氏度、0.4-8.6Mpa压缩空
+寸一致性，提升焊接质量
+短U弯头每日清洁度、中心距专项稽查通报，保证物料清洁度和尺
+规范各版块工序手套使用标准规范，提升管口清洁度:
+增加自动氮检设备和检验设备增加监控摄像头防止跳检、漏检
+置等)进行专项稽查:
+自动焊接工艺参数(氧气、天然气、氮气、枪嘴堵塞、线体固定位
+每日巡检通报各线体焊接泄漏不良情况，焊接不良比例不合格要求下班回炉培训，提升焊接技能并过程重点监控焊接质量改善情况
+每日开班对各焊检线体焊工、返修工上岗资质进行核对
+长U设备增加喷墨检测装置，识别喷墨不良管进行停报警
+检验重点检验
+针对翻遍孔毛刺长度，排查各供应商现状，自纠自查，并组织IQC
+更改为自动切割设备，提升切割稳定性
+反馈四通阀厂家进行全流程整改，输出管控措施点</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>裂管/漏氟</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>朱文锋</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>无样品仅凭照片分析，客户处确定是否有样品待我司出差分析改善</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
@@ -9783,22 +10131,22 @@
         <v>7</v>
       </c>
       <c r="AB68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -9963,6 +10311,14 @@
       </c>
       <c r="G70" s="2" t="n">
         <v>46211</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -10002,7 +10358,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>未结案</t>
+          <t>暂停</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>给客户快递200个交流接触器</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>待客户进一步提供信息/寄样回来分析后重启</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
@@ -10059,6 +10425,14 @@
       </c>
       <c r="G71" s="2" t="n">
         <v>46217</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -10104,7 +10478,44 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>未结案</t>
+          <t>结案</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">管理根因：1、针对漏贴问题：贴纸箱序列号标贴员工贴完后应自检，纸箱扫码员工应互检纸箱序列号标贴是否漏贴，实际员工自互检失效导致漏贴一张序列号标贴的不良品流出。
+核实生产信息，不良品为2026年1月27-28日W6线白班生产，‘外观检验-纸箱扫码’时间间隔未见明显异常，且不良品生产时间随机分布，不良品没有埋拉记录，均为一次过线机，该客户纸箱标贴定额均为1张，漏贴时间集中在下午6点至7点左右，分析是员工犯困或跟不上线速导致漏贴，漏贴标贴机器未及时拦截下地导致流出，当时W6线尾没有监控无法追溯详情。
+2、针对贴错问题：纸箱标贴未严格按批次隔离，员工发现纸箱标贴丢失后自行找寻纸箱标贴，从同客户另一个批次的纸箱标贴物料中找到同尾号的标贴，未核对机型号，就直接用上，导致不良品流出。
+技术根因：1月份时，W6线非大客户的纸箱序列号标贴未纳入关键件扫码管理，依赖员工自互检确认，员工粘贴有漏贴/贴错风险。2026年4月份，W6线已全部导入纸箱序列号与TCL扫码比对，以达到纸箱序列号标贴防错防漏要求。
+</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1、技术质量课提供补料所需纸箱序列号，生产安排申购纸箱序列号标贴，回料后立即提供给服务补发客户。——陈欣、张宏伟 7.4
+2、针对带纸箱序列号标贴的机型，2026年4月已将全部客户的机型纳入纸箱序列号标贴关键件扫码，各生产线尾已增加自动扫码设备。——陈欣 4.25
+3、2026年6月，中山一厂已针对序列号扫码执行情况建立专项通报机制，各线体每批次由巡检通报序列号扫码执行情况并通报到专项群，由工程师监督各线通报情况，确保序列号扫码有效落地执行。——陈欣、刘遇生、朱兴方 6.9
+</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>中山一厂</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>装配问题</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>黄敬阳</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>有</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
@@ -10119,16 +10530,16 @@
         <v>0</v>
       </c>
       <c r="AC71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -10145,7 +10556,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10154,17 +10565,25 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>46206</v>
+        <v>46216</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="G72" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="H72" s="2" t="n">
         <v>46217</v>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>变频整机</t>
+          <t>定频整机</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -10174,24 +10593,15 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>【问题描述】美国D客户反馈漏贴和错贴两个问题，问题如下：
-1、有两台外机漏贴室外机纸箱标贴，导致客户无法扫码入库。
-【型号】MXZGQ18V1EW(变频单冷)
-【订单号】MO2601132819
-【条形码】140202BPE2W16261S000002(02565626127TO0002)
-【型号】MNZGQ18V1EW（定频单冷）
-【订单号】MO2601132820
-【条形码】140202BPDFW16261S000049( 00817626127TO0049)
-2、有一台18K定频单冷室外机纸箱标贴贴成变频单冷
-【型号】条形码/铭牌型号为MNZGQ18V1EW（定频单冷）；外机错误纸箱标贴型号：MXZGQ18V1EW(变频单冷)
-【订单号】MO2601132820
-【条形码】140202BPDFW16261S000052(00817626127TO0052)
-【客户诉求】要求尽快分析改善并提供解决方案。</t>
+          <t>【问题描述】墨西哥A客户反馈我司打包带质量差，柜内发现不少打包带已经断了的现象，详见客户提供的照片和视频，要求我司分析改善。
+【参考订单号】MO2602135816/MO2604140986F/MO2602135815
+【参考柜号】TGBU9697191/TCLU1546756
+【客户需求】调查原因和改善。</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>要求尽快分析改善并提供解决方案。</t>
+          <t>调查原因和改善。</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10206,7 +10616,47 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>未结案</t>
+          <t>结案</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">综合调查，墨西哥A客户反馈的打包带断裂问题是由于打包带熔接不良导致，是多层面因素共同导致的：
+‌直接现象‌：打包带机突发故障，导致产出的打包带熔接不良。
+‌管理根因‌：外机总装线工装发生设备异常后，尚未建立完善的风险管控流程，作业人员发现设备异常后仅做临时维修，未按规范追溯排查此前已经流出的产品，导致不良品没有被及时拦截。
+‌技术根因‌：该类打包带熔接异常无法通过外观目视识别，仅能通过拉力测试检出，有限的点检频次无法完全覆盖所有故障突发的时间段，导致异常出现后没能第一时间被发现。
+</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将从生产管控、制程规范、装柜监控多个维度落地全流程改善措施，具体安排如下：
+1、验证打包带机稳定性，约打包带机厂家到厂交流设备原理及异常风险点。——李扬 7月15日
+2、与厂家交流后确认是否可以调整点检频次，在打包带机上增加计数报警功能通知人员清洁。——李扬 7月17日
+3、设备异常风险排查：编制《外机总装线工装设备异常风险控制标准指引》，组织生产、品质、工艺宣贯培训执行要求，发生设备异常后按文件对有风险的机器进行排查。——陈欣/刘志茂 7月15日
+4、仓库稽查团队重点关注打包带质量，在备货区发现打包带出现没打紧、断裂、打拧、少打的情况立即执行扫码冻结。——钱士强   持续
+5、针对该问题组织第三方物流公司宣贯，在装柜过程中发现打包带易断裂情况，立即停止装柜并向上反馈。——蒋励 2026/7/14
+</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>中山一厂</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>装配问题</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>黄敬阳</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>有</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -10221,18 +10671,270 @@
         <v>0</v>
       </c>
       <c r="AC72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>中东</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>西亚</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>定频整机</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>【问题描述】西亚H客户反馈24K和30K冷凝器破损，详见客户提供的破损照片和铭牌照片（铭牌上有对应的客户序列号）。
+1.客户条形码尾号与我司后5位一一对应；
+2.客户反馈包装箱未破损；
+3.破损位置刚好是抽管位置，暂未发现泄漏。
+【订单号】MO2510123197
+【型号】H24CH-7715 (OD)+ H30CH-7715 (OD)
+【冷凝器编码】92011-010664   845C-ⅡK7-1.4(JS) 两个机型用的是同一个冷凝器模块；
+【订单数量】4680+3510
+【不良数量】5+（客户反馈货都在经销商手上，暂没有办法统计）
+【客户需求】分析调查和改善，并提供解决方案。</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>调查原因和改善。</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>郑小平</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>客服</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>未结案</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AA73" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>拉美</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>洪都拉斯</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>定频整机</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0.1904</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>【问题描述】洪都拉斯市场反馈24K外机售后问题，外机PCB没固定住，导致短路和其它不部件损坏，订单3000套，刚出售了21套就有4套机器出现这个问题，需要我们内部紧急核查是否是批量性的问题，给出不良原因分析和改善措施的答复报告
+【订单号】MO2509121190
+【订单机型】FTAC-24CSA-T13（室外机编码Z4U20103093158）
+【订单数量】3000
+【不良数量】4
+【不良率】19.04%
+【客户诉求】客户需要我们内部紧急核查是否是批量性的问题，给出不良原因分析和改善措施的答复报告</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>客户需要我们内部紧急核查是否是批量性的问题，给出不良原因分析和改善措施的答复报告</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>曾靖衍</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>品质</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>结案</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>制造主因：飞机钉未卡到位，PCB松脱后在运输/运行振动下与周边金属件干涉短路。
+工艺次因：员工反馈难装配，工艺未评估异常影响，未启动PQE评估。
+质量次因：飞机钉未卡到位时PCB明显晃动，检验未识别，员工质量意识不足。</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>装配加严：飞机钉安装后执行回拔确认，插线岗位互检PCB固定状态。
+标准固化：编制飞机钉装配及来料检验作业指导书，明确"卡入到位、无松脱、无晃动"标准。
+培训强化：电控班开展飞机钉装配要点、回拔动作及互检要求专项培训。
+检验升级：PQC巡检频次由1小时/次缩短至30分钟/次；OQC增加PCB固定可靠性拍照检点。
+人员管控：排查电控班人员编制，落实定岗，提升待遇。</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>制造中心/制程品管部</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>装配问题</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>黄敬阳</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>待人员出差现场抽检机器确认是否存在批量问题</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AA74" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10284,7 +10986,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/海外客诉台账_标准化数据.xlsx
+++ b/海外客诉台账_标准化数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="客诉明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="数据字典" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客诉明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/海外客诉台账_标准化数据.xlsx
+++ b/海外客诉台账_标准化数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客诉明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="客诉明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="数据字典" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/海外客诉台账_标准化数据.xlsx
+++ b/海外客诉台账_标准化数据.xlsx
@@ -10767,7 +10767,7 @@
         <v>7</v>
       </c>
       <c r="AB73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC73" t="b">
         <v>0</v>
@@ -10782,7 +10782,7 @@
         <v>1</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
